--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A37"/>
+  <dimension ref="A2:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -501,182 +501,371 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>02s0k9od</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>42SH31wI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
           <t>IXMN9zkI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A64"/>
+  <dimension ref="A2:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -501,371 +501,189 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>02s0k9od</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>42SH31wI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EL1P0u6m</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
           <t>4CX22Dbk</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A38"/>
+  <dimension ref="A2:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -501,42 +501,42 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
     </row>
@@ -684,6 +684,55 @@
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>4CX22Dbk</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,316 +425,1488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A45"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
-        </is>
-      </c>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>O28yXBfT</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>toure el bilal</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0G7MtHBl</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>zaniolo nicolo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>zTWzdAKe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kostic filip</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UieHuD3i</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lovino alessio</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
-        </is>
-      </c>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
-        </is>
-      </c>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
-        </is>
-      </c>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
-        </is>
-      </c>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
-        </is>
-      </c>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
-        </is>
-      </c>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
-        </is>
-      </c>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
-        </is>
-      </c>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
-        </is>
-      </c>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
-        </is>
-      </c>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
-        </is>
-      </c>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
-        </is>
-      </c>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
-        </is>
-      </c>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
-        </is>
-      </c>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
-        </is>
-      </c>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
-        </is>
-      </c>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
-        </is>
-      </c>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
-        </is>
-      </c>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
-        </is>
-      </c>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
-        </is>
-      </c>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
-        </is>
-      </c>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
-        </is>
-      </c>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
+          <t>zVpmZBZQ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
+          <t>SSPRRTR0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
+          <t>p4dhrkCs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
+          <t>v3JgRFm3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
+          <t>dtLQNtsB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,314 +425,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A45"/>
+  <dimension ref="A2:A51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>r1mschUO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A51"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -568,216 +568,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>4CX22Dbk</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>zVpmZBZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>SSPRRTR0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>p4dhrkCs</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>v3JgRFm3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>dtLQNtsB</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Ofy73Ced</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>CGH1PgIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>21OYHBAk</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>v5l07LdU</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>fHO9ROsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>jqIIP2Cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>GUXb5YQq</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WIX2NXnS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>8x0Cb1B6</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bcZkPxo4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hernani</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>fmkHs3aU</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>morata alvaro</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +567,60 @@
           <t>GrNwFMem</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MXSXXNLr</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ebosse enzo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dQqXDhtf</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>gila mario</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>O8lwaueL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>pizarro damian</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +628,52 @@
           <t>AsIP75lK</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8Cf0NM4a</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>de vrij stefan</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>QHk1CXUh</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>martinez lautaro</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,118 +681,52 @@
           <t>6D3e2qCs</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>d4DGBiqI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fTOU6yR2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ankeye david</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6BUzxLAe</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>marcandalli alessandro</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>WOffNMWA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>matturro romero alan</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,234 +499,766 @@
           <t>player_name_miss_home_4</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KSn7To32</t>
+          <t>bHCOu1Tl</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>benedyczak adrian</t>
+          <t>gudmundsson albert</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bcZkPxo4</t>
+          <t>OSXlKkv9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hernani</t>
+          <t>pongracic marin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8UwHPuvH</t>
+          <t>tpMja0bC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>florenzi alessandro</t>
+          <t>bjarkason bjarki steinn</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>fmkHs3aU</t>
+          <t>bVamjfgm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>morata alvaro</t>
+          <t>busio gianluca</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EiVDoV04</t>
+          <t>4UOgBotB</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>sportiello marco</t>
+          <t>jajalo mato</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WpIsmaGl</t>
+          <t>vkek8Ais</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deulofeu gerard</t>
+          <t>gineitis gvidas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MXSXXNLr</t>
+          <t>v3hpfVmF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ebosse enzo</t>
+          <t>pellegri pietro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dQqXDhtf</t>
+          <t>8xFYnbEi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>gila mario</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>kolasinac sead</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O8lwaueL</t>
+          <t>bmU7ExmH</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>pizarro damian</t>
+          <t>savva zannetos</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>QgGt7V0d</t>
+          <t>ARdXOcOJ</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4ryWOtME</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>vlasic nikola</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0G7MtHBl</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>zaniolo nicolo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>G62SXlFI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8Cf0NM4a</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>de vrij stefan</t>
-        </is>
-      </c>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>lIjZ6yI2</t>
+          <t>KbPlg3Fl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>QHk1CXUh</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>martinez lautaro</t>
-        </is>
-      </c>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>E7Jj74nK</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>grassi alberto</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6HUZxS6p</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>perisan samuele</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Ees7JNmc</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>80NWC6K6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>cambiaghi nicolo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6BUzxLAe</t>
+          <t>8CI4QAT5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>marcandalli alessandro</t>
+          <t>el azzouzi oussama</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>Q995M7Dt</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>ferguson lewis</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6kvbBHqr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jankto jakub</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0zd8jKI5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>mazzitelli luca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>t20vQIvC</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>varane raphael</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>zTWzdAKe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>kostic filip</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>bDU1sgDT</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>thuram kephren</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4KWCbTaQ</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>weah timothy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,539 +441,245 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_2</t>
+          <t>id_player_miss_away_1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_2</t>
+          <t>player_name_miss_away_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_1</t>
+          <t>id_player_miss_away_2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_1</t>
+          <t>player_name_miss_away_2</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_2</t>
+          <t>id_player_miss_away_3</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_2</t>
+          <t>player_name_miss_away_3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_3</t>
+          <t>id_player_miss_away_4</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_3</t>
+          <t>player_name_miss_away_4</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_3</t>
+          <t>id_player_miss_away_5</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
           <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bHCOu1Tl</t>
+          <t>6kvbBHqr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gudmundsson albert</t>
+          <t>jankto jakub</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OSXlKkv9</t>
+          <t>0zd8jKI5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pongracic marin</t>
+          <t>mazzitelli luca</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>tpMja0bC</t>
+          <t>t20vQIvC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bjarkason bjarki steinn</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>bVamjfgm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>busio gianluca</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4UOgBotB</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>jajalo mato</t>
-        </is>
-      </c>
+          <t>varane raphael</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vkek8Ais</t>
+          <t>ImoJ2c3M</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gineitis gvidas</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>v3hpfVmF</t>
+          <t>zTWzdAKe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>pellegri pietro</t>
+          <t>kostic filip</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8xFYnbEi</t>
+          <t>EskCwiLE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>kolasinac sead</t>
+          <t>milik arkadiusz</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hvC4gron</t>
+          <t>MTNGv0hT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>scalvini giorgio</t>
+          <t>pogba paul</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>vDgQxOYl</t>
+          <t>bDU1sgDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>scamacca gianluca</t>
+          <t>thuram kephren</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>bmU7ExmH</t>
+          <t>4KWCbTaQ</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>savva zannetos</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ARdXOcOJ</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4ryWOtME</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>vlasic nikola</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>QB1RMomj</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>toloi rafael</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0G7MtHBl</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>zaniolo nicolo</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+          <t>weah timothy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KbPlg3Fl</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ebuehi tyronne</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>E7Jj74nK</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>grassi alberto</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6HUZxS6p</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>perisan samuele</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Ees7JNmc</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>zurkowski szymon</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>80NWC6K6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>cambiaghi nicolo</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>8CI4QAT5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>el azzouzi oussama</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Q995M7Dt</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ferguson lewis</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6kvbBHqr</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>jankto jakub</t>
-        </is>
-      </c>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0zd8jKI5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>mazzitelli luca</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>t20vQIvC</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>varane raphael</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>zTWzdAKe</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>kostic filip</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>EskCwiLE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>tSUumbUT</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>miretti fabio</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>bDU1sgDT</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>thuram kephren</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>4KWCbTaQ</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>weah timothy</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -988,21 +694,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1017,21 +713,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1046,21 +732,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1075,21 +751,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1104,21 +770,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1133,132 +789,6 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,169 +441,223 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6kvbBHqr</t>
+          <t>tpMja0bC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jankto jakub</t>
+          <t>bjarkason bjarki steinn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0zd8jKI5</t>
+          <t>bVamjfgm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>mazzitelli luca</t>
+          <t>busio gianluca</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>t20vQIvC</t>
+          <t>4UOgBotB</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>varane raphael</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>jajalo mato</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vkek8Ais</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>gineitis gvidas</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bmU7ExmH</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>savva zannetos</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4ryWOtME</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vlasic nikola</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ImoJ2c3M</t>
+          <t>G62SXlFI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cruz juan</t>
+          <t>buchanan tajon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>zTWzdAKe</t>
+          <t>8Cf0NM4a</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kostic filip</t>
+          <t>de vrij stefan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EskCwiLE</t>
+          <t>QHk1CXUh</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>milik arkadiusz</t>
+          <t>martinez lautaro</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MTNGv0hT</t>
+          <t>8xFYnbEi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>pogba paul</t>
+          <t>kolasinac sead</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bDU1sgDT</t>
+          <t>hvC4gron</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>thuram kephren</t>
+          <t>scalvini giorgio</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4KWCbTaQ</t>
+          <t>vDgQxOYl</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>weah timothy</t>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -618,11 +672,13 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -637,11 +693,13 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -656,11 +714,13 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -675,11 +735,13 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -694,11 +756,13 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -713,11 +777,13 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -732,11 +798,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -751,44 +819,8 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,224 +461,240 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tpMja0bC</t>
+          <t>80NWC6K6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bjarkason bjarki steinn</t>
+          <t>cambiaghi nicolo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bVamjfgm</t>
+          <t>8CI4QAT5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>busio gianluca</t>
+          <t>el azzouzi oussama</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4UOgBotB</t>
+          <t>Q995M7Dt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>jajalo mato</t>
+          <t>ferguson lewis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>vkek8Ais</t>
+          <t>EmmpFCXN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>gineitis gvidas</t>
+          <t>ndoye dan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bmU7ExmH</t>
+          <t>KbPlg3Fl</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>savva zannetos</t>
+          <t>ebuehi tyronne</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ARdXOcOJ</t>
+          <t>6HUZxS6p</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>schuurs perr</t>
+          <t>perisan samuele</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4ryWOtME</t>
+          <t>Ees7JNmc</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>vlasic nikola</t>
-        </is>
-      </c>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G62SXlFI</t>
+          <t>lIjZ6yI2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>8Cf0NM4a</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>de vrij stefan</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>QHk1CXUh</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>martinez lautaro</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>8xFYnbEi</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>kolasinac sead</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>hvC4gron</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>scalvini giorgio</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>vDgQxOYl</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>scamacca gianluca</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>QB1RMomj</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>toloi rafael</t>
-        </is>
-      </c>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dQqXDhtf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>gila mario</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>fmkHs3aU</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>morata alvaro</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -689,138 +705,300 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bcZkPxo4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>hernani</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bHCOu1Tl</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gudmundsson albert</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fTOU6yR2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ankeye david</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vgmL526e</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bani mattia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WOffNMWA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>matturro romero alan</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n53v4sSd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chico conceicao</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>zTWzdAKe</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>kostic filip</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>hC5yfF2A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>le fee enzo</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>bDU1sgDT</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>thuram kephren</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4KWCbTaQ</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>weah timothy</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MXSXXNLr</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ebosse enzo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KEZVn6fB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>kamara hassane</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O8lwaueL</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>pizarro damian</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t20vQIvC</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>varane raphael</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,80 +441,60 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_2</t>
+          <t>id_player_miss_home_5</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_2</t>
+          <t>player_name_miss_home_5</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_3</t>
+          <t>id_player_miss_home_6</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_6</t>
         </is>
@@ -523,482 +503,254 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80NWC6K6</t>
+          <t>bHCOu1Tl</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cambiaghi nicolo</t>
+          <t>gudmundsson albert</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8CI4QAT5</t>
+          <t>ENDYjGK9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>el azzouzi oussama</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Q995M7Dt</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ferguson lewis</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EmmpFCXN</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ndoye dan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>KbPlg3Fl</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ebuehi tyronne</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6HUZxS6p</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>perisan samuele</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Ees7JNmc</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>zurkowski szymon</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lIjZ6yI2</t>
+          <t>fTOU6yR2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>ankeye david</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vgmL526e</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>bani mattia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WOffNMWA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>matturro romero alan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dQqXDhtf</t>
+          <t>zTWzdAKe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gila mario</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>kostic filip</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>hC5yfF2A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>le fee enzo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8UwHPuvH</t>
+          <t>bDU1sgDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>florenzi alessandro</t>
+          <t>thuram kephren</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>fmkHs3aU</t>
+          <t>4KWCbTaQ</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>morata alvaro</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>EiVDoV04</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>sportiello marco</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>weah timothy</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>t20vQIvC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>varane raphael</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MXSXXNLr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ebosse enzo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KEZVn6fB</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>kamara hassane</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>KSn7To32</t>
+          <t>O8lwaueL</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>benedyczak adrian</t>
+          <t>pizarro damian</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>bcZkPxo4</t>
+          <t>QgGt7V0d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>hernani</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>bHCOu1Tl</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>gudmundsson albert</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>fTOU6yR2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ankeye david</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vgmL526e</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>bani mattia</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>WOffNMWA</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>matturro romero alan</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>tSUumbUT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>miretti fabio</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>xjWe0TTo</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>zanoli alessandro</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>n53v4sSd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>chico conceicao</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>zTWzdAKe</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>kostic filip</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>EskCwiLE</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>hC5yfF2A</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>le fee enzo</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>bDU1sgDT</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>thuram kephren</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>4KWCbTaQ</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>weah timothy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>WpIsmaGl</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>deulofeu gerard</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MXSXXNLr</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ebosse enzo</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KEZVn6fB</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>kamara hassane</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>O8lwaueL</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>pizarro damian</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>t20vQIvC</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>varane raphael</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>QgGt7V0d</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
           <t>sanchez alexis</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>jaNZBJgT</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>toure souleymane</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,330 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A2:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bHCOu1Tl</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>gudmundsson albert</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>fTOU6yR2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ankeye david</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vgmL526e</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>bani mattia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>WOffNMWA</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>matturro romero alan</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>tSUumbUT</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>miretti fabio</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>xjWe0TTo</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>zanoli alessandro</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>zTWzdAKe</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>kostic filip</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>hC5yfF2A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>le fee enzo</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>EskCwiLE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bDU1sgDT</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>thuram kephren</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>4KWCbTaQ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>weah timothy</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WpIsmaGl</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deulofeu gerard</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>t20vQIvC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>varane raphael</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MXSXXNLr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ebosse enzo</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KEZVn6fB</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>kamara hassane</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>O8lwaueL</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>pizarro damian</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>QgGt7V0d</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>jaNZBJgT</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>toure souleymane</t>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A11"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -498,6 +498,76 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,148 +425,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
-        </is>
-      </c>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fTOU6yR2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ankeye david</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>63jp0ZJd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>norton cuffy brooke</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
-        </is>
-      </c>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pW01mTt9</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>djimsiti berat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SQjcKLRk</t>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4ryWOtME</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vlasic nikola</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sf4eaXAH</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>dorgu patrick</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
-        </is>
-      </c>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WMeojevP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>prati matteo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>bcZkPxo4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hernani</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4bDDVvmT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>suzuki zion</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>jaNZBJgT</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>toure souleymane</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
           <t>rgFQPs4S</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2ucWYubt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>44gmVcc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>S66wtFBN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Yqo4RFdU</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>O8QDoJsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>A50vXJSh</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pOEMqcCb</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>WvDUsysB</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,419 +425,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>fTOU6yR2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ankeye david</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8l36RdAF</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>messias junior</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>tSUumbUT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>miretti fabio</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>63jp0ZJd</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>norton cuffy brooke</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>xjWe0TTo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>zanoli alessandro</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pW01mTt9</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>djimsiti berat</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>hvC4gron</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>scalvini giorgio</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vDgQxOYl</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>scamacca gianluca</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ARdXOcOJ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4ryWOtME</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>vlasic nikola</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Sf4eaXAH</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>dorgu patrick</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>lIjZ6yI2</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>kaba mohamed</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WMeojevP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>prati matteo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>CnvwSKf9</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rui mario</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>p8mcxZnq</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ciurria patrick</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>G62SXlFI</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>KSn7To32</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>benedyczak adrian</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6NqFKJLp</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>estevez nahuel</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>bcZkPxo4</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>hernani</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4bDDVvmT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>suzuki zion</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>QgGt7V0d</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>jaNZBJgT</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>toure souleymane</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,146 +425,578 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
-        </is>
-      </c>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>rJcy0auH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>nicolussi hans</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>fTOU6yR2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ankeye david</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>63jp0ZJd</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>norton cuffy brooke</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
-        </is>
-      </c>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>n53v4sSd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chico conceicao</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
-        </is>
-      </c>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UevlGWN5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>keita mandela</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>l8UQT6rE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>valeri emanuele</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
-        </is>
-      </c>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>80NWC6K6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cambiaghi nicolo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Q995M7Dt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ferguson lewis</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>f1Ft78yl</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>gagliardini roberto</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0WK0EKMu</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>vignato samuel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
-        </is>
-      </c>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
-        </is>
-      </c>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KS8ySjGG</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0vSsR1xI</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>thiaw malick</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
           <t>OAeKROjD</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>nD7QhgLn</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>godfrey ben</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KSz457vB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>barba federico</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>t20vQIvC</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>varane raphael</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,359 +461,141 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_4</t>
+          <t>id_player_miss_away_1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>hvC4gron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>scalvini giorgio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8l36RdAF</t>
+          <t>vDgQxOYl</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>messias junior</t>
+          <t>scamacca gianluca</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>tSUumbUT</t>
+          <t>QB1RMomj</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>miretti fabio</t>
+          <t>toloi rafael</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>63jp0ZJd</t>
+          <t>t20vQIvC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>norton cuffy brooke</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>xjWe0TTo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>zanoli alessandro</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>varane raphael</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pW01mTt9</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>djimsiti berat</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>hvC4gron</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>scalvini giorgio</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>vDgQxOYl</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>scamacca gianluca</t>
-        </is>
-      </c>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ARdXOcOJ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4ryWOtME</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>vlasic nikola</t>
-        </is>
-      </c>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Sf4eaXAH</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>dorgu patrick</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>lIjZ6yI2</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WMeojevP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>prati matteo</t>
-        </is>
-      </c>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>CnvwSKf9</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rui mario</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>p8mcxZnq</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ciurria patrick</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>G62SXlFI</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>KSn7To32</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>benedyczak adrian</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6NqFKJLp</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>estevez nahuel</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>bcZkPxo4</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>hernani</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4bDDVvmT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>suzuki zion</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>QgGt7V0d</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>jaNZBJgT</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>toure souleymane</t>
-        </is>
-      </c>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -824,20 +606,216 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,10 +461,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
@@ -478,344 +488,54 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>nD7QhgLn</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>godfrey ben</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>hvC4gron</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>scalvini giorgio</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>vDgQxOYl</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>scamacca gianluca</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>QB1RMomj</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>toloi rafael</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>t20vQIvC</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>varane raphael</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,361 +461,685 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hvC4gron</t>
+          <t>KS8ySjGG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scalvini giorgio</t>
+          <t>bennacer ismael</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vDgQxOYl</t>
+          <t>OKPvQBOR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>scamacca gianluca</t>
+          <t>calabria davide</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>QB1RMomj</t>
+          <t>8UwHPuvH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>toloi rafael</t>
+          <t>florenzi alessandro</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>t20vQIvC</t>
+          <t>EDhpumvd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>varane raphael</t>
-        </is>
-      </c>
+          <t>okafor noah</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0vSsR1xI</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>thiaw malick</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6TtQuJeb</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>guilbert frederic</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>W0yrjzz2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>barella nicolo</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>63jp0ZJd</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>norton cuffy brooke</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>YBPBtjuL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>adzic vasilije</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4KWCbTaQ</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>weah timothy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80NWC6K6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cambiaghi nicolo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q995M7Dt</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ferguson lewis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>06IMJkrL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pobega tommaso</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CS7XFNwq</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ilkhan emirhan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bmU7ExmH</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>savva zannetos</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4ryWOtME</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>vlasic nikola</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>G8cfGd8h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>gigot samuel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hC5yfF2A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>le fee enzo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8GVcLWJk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pellegrini lorenzo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KSz457vB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>barba federico</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>hh5m41l6</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>dawidowicz pawel</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>nJ2Rd9i9</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>harroui abdou</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>WrzFSvEm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>serdar suat</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KbPlg3Fl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>b3uylvFN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>fazzini jacopo</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EBsz2tTd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>meret alex</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>f1Ft78yl</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>gagliardini roberto</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0WK0EKMu</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>vignato samuel</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_5</t>
+          <t>id_player_miss_away_1</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_5</t>
+          <t>player_name_miss_away_1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_6</t>
+          <t>id_player_miss_away_2</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_6</t>
+          <t>player_name_miss_away_2</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_1</t>
+          <t>id_player_miss_away_3</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_1</t>
+          <t>player_name_miss_away_3</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_2</t>
+          <t>id_player_miss_away_4</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
@@ -533,613 +513,324 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KS8ySjGG</t>
+          <t>CS7XFNwq</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bennacer ismael</t>
+          <t>ilkhan emirhan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OKPvQBOR</t>
+          <t>bmU7ExmH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>calabria davide</t>
+          <t>savva zannetos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8UwHPuvH</t>
+          <t>ARdXOcOJ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>florenzi alessandro</t>
+          <t>schuurs perr</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>EDhpumvd</t>
+          <t>4ryWOtME</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>okafor noah</t>
+          <t>vlasic nikola</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EiVDoV04</t>
+          <t>G8cfGd8h</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>sportiello marco</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0vSsR1xI</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>thiaw malick</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>6TtQuJeb</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>guilbert frederic</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>lIjZ6yI2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>gigot samuel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WpIsmaGl</t>
+          <t>hC5yfF2A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deulofeu gerard</t>
+          <t>le fee enzo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QgGt7V0d</t>
+          <t>n5cPVwks</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sanchez alexis</t>
+          <t>saelemaekers alexis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>W0yrjzz2</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>barella nicolo</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>G62SXlFI</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GGkyU0bT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>malinovsky ruslan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>63jp0ZJd</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>norton cuffy brooke</t>
-        </is>
-      </c>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hh5m41l6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>dawidowicz pawel</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>YBPBtjuL</t>
+          <t>nJ2Rd9i9</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>adzic vasilije</t>
+          <t>harroui abdou</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>EskCwiLE</t>
+          <t>WrzFSvEm</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>4KWCbTaQ</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>weah timothy</t>
+          <t>serdar suat</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80NWC6K6</t>
+          <t>KbPlg3Fl</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cambiaghi nicolo</t>
+          <t>ebuehi tyronne</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q995M7Dt</t>
+          <t>t2MszR74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ferguson lewis</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>06IMJkrL</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>pobega tommaso</t>
-        </is>
-      </c>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>hvC4gron</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>scalvini giorgio</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>vDgQxOYl</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>scamacca gianluca</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>QB1RMomj</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>toloi rafael</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CS7XFNwq</t>
+          <t>EBsz2tTd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ilkhan emirhan</t>
+          <t>meret alex</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bmU7ExmH</t>
+          <t>CnvwSKf9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>savva zannetos</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ARdXOcOJ</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4ryWOtME</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>vlasic nikola</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>G8cfGd8h</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>gigot samuel</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>gagliardini roberto</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0WK0EKMu</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>vignato samuel</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hC5yfF2A</t>
+          <t>KSn7To32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>le fee enzo</t>
+          <t>benedyczak adrian</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8GVcLWJk</t>
+          <t>x0EJsbc8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>pellegrini lorenzo</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>n5cPVwks</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>saelemaekers alexis</t>
-        </is>
-      </c>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>WMeojevP</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>prati matteo</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>tpMja0bC</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>bjarkason bjarki steinn</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>KSz457vB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>barba federico</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>hh5m41l6</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>dawidowicz pawel</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>nJ2Rd9i9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>harroui abdou</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>WrzFSvEm</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>serdar suat</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>KbPlg3Fl</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ebuehi tyronne</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>b3uylvFN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>fazzini jacopo</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EBsz2tTd</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>meret alex</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CnvwSKf9</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>rui mario</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>p8mcxZnq</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>ciurria patrick</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>f1Ft78yl</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>gagliardini roberto</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0WK0EKMu</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>vignato samuel</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,40 +471,60 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
@@ -513,324 +533,742 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CS7XFNwq</t>
+          <t>EBsz2tTd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ilkhan emirhan</t>
+          <t>meret alex</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bmU7ExmH</t>
+          <t>CnvwSKf9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>savva zannetos</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ARdXOcOJ</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4ryWOtME</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>vlasic nikola</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>G8cfGd8h</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>gigot samuel</t>
-        </is>
-      </c>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hC5yfF2A</t>
+          <t>ImoJ2c3M</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>le fee enzo</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>n5cPVwks</t>
+          <t>hh5m41l6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>saelemaekers alexis</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>dawidowicz pawel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>nJ2Rd9i9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>harroui abdou</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WrzFSvEm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>serdar suat</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>CQDgdTbJ</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>suslov tomas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>tpMja0bC</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>bjarkason bjarki steinn</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>tjm4dqgg</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>duncan alfred</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GdjB2qGA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kristensen thomas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hh5m41l6</t>
+          <t>lIjZ6yI2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>dawidowicz pawel</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>nJ2Rd9i9</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>harroui abdou</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>WrzFSvEm</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>serdar suat</t>
-        </is>
-      </c>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KbPlg3Fl</t>
+          <t>lt87Q6nj</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ebuehi tyronne</t>
+          <t>brescianini marco</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>t2MszR74</t>
+          <t>hvC4gron</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sazonov saba</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EBsz2tTd</t>
+          <t>W0yrjzz2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>meret alex</t>
+          <t>barella nicolo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CnvwSKf9</t>
+          <t>G62SXlFI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rui mario</t>
+          <t>buchanan tajon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>p8mcxZnq</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ciurria patrick</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ENDYjGK9</t>
+          <t>CS7XFNwq</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>cragno alessio</t>
+          <t>ilkhan emirhan</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>f1Ft78yl</t>
+          <t>bmU7ExmH</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>gagliardini roberto</t>
+          <t>savva zannetos</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0WK0EKMu</t>
+          <t>ARdXOcOJ</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>vignato samuel</t>
-        </is>
-      </c>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KSn7To32</t>
+          <t>YBPBtjuL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>benedyczak adrian</t>
+          <t>adzic vasilije</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>x0EJsbc8</t>
+          <t>INWVBb0R</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>circati alessandro</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>bremer</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>4KWCbTaQ</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>weah timothy</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>WMeojevP</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>prati matteo</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>80NWC6K6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cambiaghi nicolo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A9WpvRff</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>de silvestri lorenzo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8CI4QAT5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>el azzouzi oussama</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Q995M7Dt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ferguson lewis</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O8NaVz3G</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>lucumi jhon</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>06IMJkrL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>pobega tommaso</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G8cfGd8h</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gigot samuel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>KbPlg3Fl</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>f1Ft78yl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>gagliardini roberto</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0WK0EKMu</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>vignato samuel</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hC5yfF2A</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>le fee enzo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>UL36DwiA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bartesaghi davide</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>KS8ySjGG</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,44 +481,44 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
@@ -527,410 +527,414 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EBsz2tTd</t>
+          <t>YBPBtjuL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>meret alex</t>
+          <t>adzic vasilije</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CnvwSKf9</t>
+          <t>INWVBb0R</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>rui mario</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>bremer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>filNjPIq</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gonzalez nicolas ivan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4KWCbTaQ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>weah timothy</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WMeojevP</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>prati matteo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ImoJ2c3M</t>
+          <t>80NWC6K6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cruz juan</t>
+          <t>cambiaghi nicolo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hh5m41l6</t>
+          <t>A9WpvRff</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>dawidowicz pawel</t>
+          <t>de silvestri lorenzo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nJ2Rd9i9</t>
+          <t>8CI4QAT5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>harroui abdou</t>
+          <t>el azzouzi oussama</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WrzFSvEm</t>
+          <t>Q995M7Dt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>serdar suat</t>
+          <t>ferguson lewis</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CQDgdTbJ</t>
+          <t>O8NaVz3G</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>suslov tomas</t>
+          <t>lucumi jhon</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tpMja0bC</t>
+          <t>06IMJkrL</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bjarkason bjarki steinn</t>
+          <t>pobega tommaso</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>tjm4dqgg</t>
+          <t>KSn7To32</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>duncan alfred</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>WpIsmaGl</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deulofeu gerard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GdjB2qGA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>kristensen thomas</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ChzBGkMR</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>payero martin</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>QgGt7V0d</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>lIjZ6yI2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>KbPlg3Fl</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lt87Q6nj</t>
+          <t>p8mcxZnq</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brescianini marco</t>
+          <t>ciurria patrick</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hvC4gron</t>
+          <t>ENDYjGK9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>scalvini giorgio</t>
+          <t>cragno alessio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>vDgQxOYl</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>scamacca gianluca</t>
+          <t>gagliardini roberto</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>QB1RMomj</t>
+          <t>0WK0EKMu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>toloi rafael</t>
+          <t>vignato samuel</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GGkyU0bT</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>malinovsky ruslan</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8l36RdAF</t>
+          <t>hC5yfF2A</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>messias junior</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+          <t>le fee enzo</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W0yrjzz2</t>
+          <t>v9oBM840</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>barella nicolo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>G62SXlFI</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
+          <t>mandragora rolando</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>CS7XFNwq</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ilkhan emirhan</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>bmU7ExmH</t>
+          <t>UL36DwiA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>savva zannetos</t>
+          <t>bartesaghi davide</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ARdXOcOJ</t>
+          <t>KS8ySjGG</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>OKPvQBOR</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>calabria davide</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>YBPBtjuL</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>adzic vasilije</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>INWVBb0R</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>bremer</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>EskCwiLE</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>4KWCbTaQ</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>weah timothy</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>WMeojevP</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>prati matteo</t>
-        </is>
-      </c>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -939,114 +943,46 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>80NWC6K6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>cambiaghi nicolo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>A9WpvRff</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>de silvestri lorenzo</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>8CI4QAT5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>el azzouzi oussama</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Q995M7Dt</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ferguson lewis</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>O8NaVz3G</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>lucumi jhon</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>KSn7To32</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>benedyczak adrian</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>x0EJsbc8</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>circati alessandro</t>
-        </is>
-      </c>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>06IMJkrL</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>pobega tommaso</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>G8cfGd8h</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>gigot samuel</t>
-        </is>
-      </c>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -1055,112 +991,52 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>KbPlg3Fl</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ebuehi tyronne</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>t2MszR74</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>sazonov saba</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>p8mcxZnq</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ciurria patrick</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>f1Ft78yl</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>gagliardini roberto</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0WK0EKMu</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>vignato samuel</t>
-        </is>
-      </c>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hC5yfF2A</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>le fee enzo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>n5cPVwks</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>saelemaekers alexis</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1173,53 +1049,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>UL36DwiA</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bartesaghi davide</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>KS8ySjGG</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>bennacer ismael</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>8UwHPuvH</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>florenzi alessandro</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>EiVDoV04</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>sportiello marco</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1242,11 +1088,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1269,6 +1117,66 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A24"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Cl5M5C3L</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SUqEqOY3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>coulibaly woyo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +635,98 @@
           <t>EXLhbUee</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>80NWC6K6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cambiaghi nicolo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8CI4QAT5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>el azzouzi oussama</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Q995M7Dt</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ferguson lewis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CtdcoETk</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ekuban caleb</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>06IMJkrL</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>pobega tommaso</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +734,106 @@
           <t>SznSCTAl</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GdjB2qGA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kristensen thomas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2oBl3y29</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>lovric sandi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KS8ySjGG</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ATurLHr0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>hernandez theo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +841,106 @@
           <t>2g2mKBIE</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YBPBtjuL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>adzic vasilije</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>INWVBb0R</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>bremer</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>n53v4sSd</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>chico conceicao</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>filNjPIq</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>gonzalez nicolas ivan</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>lOCjQkeo</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>koopmeiners teun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>jZHxRi2A</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>mckennie weston</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4KWCbTaQ</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>weah timothy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +948,34 @@
           <t>8Kjh0jRr</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +983,34 @@
           <t>AJ5eIkmR</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1018,34 @@
           <t>dGwq9oAD</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1053,34 @@
           <t>GMBD7YY8</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1088,34 @@
           <t>0lpzB7u1</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +1123,34 @@
           <t>McP0d8Q7</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +1158,34 @@
           <t>I5fXHFho</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +1193,34 @@
           <t>bLD0NyVN</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +1228,34 @@
           <t>UuMqRJVb</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +1263,34 @@
           <t>8f71RSPs</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +1298,34 @@
           <t>OMVUWl2K</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +1333,34 @@
           <t>jeAhPc0B</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +1368,34 @@
           <t>OjcQLOgJ</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +1403,34 @@
           <t>xY3xTu1n</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -560,6 +1438,34 @@
           <t>jwaINpP6</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -567,6 +1473,34 @@
           <t>fB59P6ff</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -574,6 +1508,34 @@
           <t>Ug79dz7j</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -581,6 +1543,34 @@
           <t>4CLi9Djd</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -588,6 +1578,209 @@
           <t>WIDwXGr3</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,6 +567,16 @@
       <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
@@ -628,6 +638,8 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -727,6 +739,8 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -834,6 +848,8 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -941,6 +957,8 @@
           <t>weah timothy</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -948,16 +966,56 @@
           <t>8Kjh0jRr</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0Qcw6Yy1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lobotka stanislav</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EBsz2tTd</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>meret alex</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KbPlg3Fl</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -976,6 +1034,8 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -983,14 +1043,30 @@
           <t>AJ5eIkmR</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1011,6 +1087,8 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1018,24 +1096,80 @@
           <t>dGwq9oAD</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lt87Q6nj</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>brescianini marco</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pW01mTt9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>djimsiti berat</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SzDIipZ9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>kossounou odilon</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>tjm4dqgg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>duncan alfred</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1046,6 +1180,16 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1081,6 +1225,8 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1116,6 +1262,8 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1151,6 +1299,8 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1186,6 +1336,8 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1221,6 +1373,8 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1256,6 +1410,8 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1291,6 +1447,8 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1326,6 +1484,8 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1361,6 +1521,8 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1396,6 +1558,8 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1431,6 +1595,8 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1466,6 +1632,8 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1501,6 +1669,8 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1536,6 +1706,8 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1571,6 +1743,8 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1606,6 +1780,8 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1641,6 +1817,8 @@
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1676,6 +1854,8 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1711,6 +1891,8 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1746,6 +1928,8 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1781,6 +1965,82 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A31"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_10</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_10</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>I5fXHFho</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GdjB2qGA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kristensen thomas</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SMbMSc26</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>thauvin florian</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6kvbBHqr</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>jankto jakub</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>K0nUrV5K</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>lapadula gianluca</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>YZEkc9qD</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>obert adam</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>xrQ22VYn</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>pavoletti leonardo</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>8xR8lIU9</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>wieteska mateusz</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +771,158 @@
           <t>bLD0NyVN</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hM1aIsWB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ciammaglichella aaron</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CS7XFNwq</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ilkhan emirhan</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UZiNdd1Q</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>maripan guillermo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vwnI8wkF</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nije eybi</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bmU7ExmH</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>savva zannetos</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Uaabio2H</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>van der brempt ignace</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>KSz457vB</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>barba federico</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>IBUaxPl6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>cerri alberto</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>W2R804U4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>roberto sergi</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>v7zQxVoD</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>zapata duvan</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>vqZMiS0h</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>illic ivan</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4vTK4LUr</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sosa borna</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>nRc0fR5f</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>tameze adrien</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,195 +930,928 @@
           <t>UuMqRJVb</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0Qcw6Yy1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lobotka stanislav</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EBsz2tTd</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>meret alex</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4fbjCD7B</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>berisha medon</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>GxXIRkFl</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>gallo antonino</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0xAp4q1P</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>gonzalez joan</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>8xArOHfB</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>sansone nicola</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>IoRXiRdq</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>banda lameck</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>SE59rbUO</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>bonifazi kevin</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>vVyq9D0S</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>burnete catalin</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>4jKQUIgi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>hasa luis</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>lIjZ6yI2</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>bygrxvpg</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>marchwinski filip</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8f71RSPs</t>
-        </is>
-      </c>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lt87Q6nj</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>brescianini marco</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SzDIipZ9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>kossounou odilon</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>QB1RMomj</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>toloi rafael</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>6JBYdeU4</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>duda ondrej</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CERvOK0k</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>frese martin</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>nJ2Rd9i9</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>harroui abdou</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>AZfDAIPf</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>alidou faride</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>hh5m41l6</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>dawidowicz pawel</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>A1vJjksK</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lambourde mathis</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>WrzFSvEm</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>serdar suat</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
-        </is>
-      </c>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>WU5civJO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>kowalski mateusz</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>KbPlg3Fl</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>QiCirDVf</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>belardinelli luca</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CnRzW1VM</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>maleh youssef</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6HUZxS6p</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>perisan samuele</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Ees7JNmc</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
-        </is>
-      </c>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6ZesE86o</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>guendouzi matteo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WlqJxlIT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lazzari manuel</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wr49C0j4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>romagnoli alessio</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CtdcoETk</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ekuban caleb</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AazXYT3h</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>vitinha</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>vgmL526e</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>bani mattia</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>EFmPm0Qo</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>de winter koni</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>vZY7FZwP</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>gollini pierluigi</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>63jp0ZJd</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>norton cuffy brooke</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
-        </is>
-      </c>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>f1Ft78yl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>gagliardini roberto</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>txSCnXec</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>maldini daniel</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MRq91oVQ</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>petagna andrea</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>dbqlLrFU</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sensi stefano</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>tjm4dqgg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>duncan alfred</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>GdRRPoEK</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>turati stefano</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
-        </is>
-      </c>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SrhnSpzL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>acerbi francesco</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IRQeP5FJ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>calhanoglu hakan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>QZQkZOWj</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>carlos augusto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hzUi0u2S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>asllani kristjan</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>INWVBb0R</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>bremer</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>IZxlmmuF</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>douglas luiz</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>filNjPIq</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>gonzalez nicolas ivan</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>lOCjQkeo</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>koopmeiners teun</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
           <t>fB59P6ff</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Ug79dz7j</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4CLi9Djd</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WIDwXGr3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IFm4IHT9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0b5fTYsS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Y96v2dqT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>rcXrBZLq</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>EssDGebM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Sp7nVfDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>p2kdKwac</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>pOryx3Qa</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Gpn0zjke</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>CCu9YTJ7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>b7pTwPem</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>WvkEqfS8</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>v5hMsYdL</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>jqCRLjz2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>vJXfdXBE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>rXmhxCKr</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bHCOu1Tl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gudmundsson albert</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>v9oBM840</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mandragora rolando</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OSXlKkv9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>pongracic marin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>QPclX9Uq</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>kean moise</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>fFLge2V1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>el shaarawy stephan</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>W4myUVXR</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>dybala paulo</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,273 +481,251 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_6</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_6</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_7</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_7</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_8</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_8</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_9</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_9</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_10</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_10</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_7</t>
+          <t>id_player_miss_away_8</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
           <t>player_name_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_9</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_9</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_10</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WpIsmaGl</t>
+          <t>zaVrgWQt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deulofeu gerard</t>
+          <t>makoumbou antoine</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GdjB2qGA</t>
+          <t>6kvbBHqr</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kristensen thomas</t>
+          <t>jankto jakub</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>QgGt7V0d</t>
+          <t>K0nUrV5K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>sanchez alexis</t>
+          <t>lapadula gianluca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SMbMSc26</t>
+          <t>tvxzDyfa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>thauvin florian</t>
+          <t>mutandwa kingstone</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>8xR8lIU9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>wieteska mateusz</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ChzBGkMR</t>
+          <t>MiXFJwit</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>payero martin</t>
+          <t>aebischer michel</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6kvbBHqr</t>
+          <t>80NWC6K6</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>jankto jakub</t>
+          <t>cambiaghi nicolo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>K0nUrV5K</t>
+          <t>8CI4QAT5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>lapadula gianluca</t>
+          <t>el azzouzi oussama</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>YZEkc9qD</t>
+          <t>n9FYAE96</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>obert adam</t>
+          <t>erlic martin</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>xrQ22VYn</t>
+          <t>Q995M7Dt</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>pavoletti leonardo</t>
+          <t>ferguson lewis</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>8xR8lIU9</t>
+          <t>EmmpFCXN</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>wieteska mateusz</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+          <t>ndoye dan</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>hxdzXUCO</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>lykogiannis charalampos</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
@@ -758,572 +736,516 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hM1aIsWB</t>
+          <t>0xAp4q1P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ciammaglichella aaron</t>
+          <t>gonzalez joan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CS7XFNwq</t>
+          <t>8xArOHfB</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ilkhan emirhan</t>
+          <t>sansone nicola</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UZiNdd1Q</t>
+          <t>4fbjCD7B</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>maripan guillermo</t>
+          <t>berisha medon</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>vwnI8wkF</t>
+          <t>SE59rbUO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nije eybi</t>
+          <t>bonifazi kevin</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bmU7ExmH</t>
+          <t>vVyq9D0S</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>savva zannetos</t>
+          <t>burnete catalin</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ARdXOcOJ</t>
+          <t>ImoJ2c3M</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>schuurs perr</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Uaabio2H</t>
+          <t>hh5m41l6</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>van der brempt ignace</t>
+          <t>dawidowicz pawel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KSz457vB</t>
+          <t>CERvOK0k</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>barba federico</t>
+          <t>frese martin</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>IBUaxPl6</t>
+          <t>nJ2Rd9i9</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>cerri alberto</t>
+          <t>harroui abdou</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>W2R804U4</t>
+          <t>AZfDAIPf</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>roberto sergi</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>v7zQxVoD</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>zapata duvan</t>
-        </is>
-      </c>
+          <t>alidou faride</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>nuvpd81D</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>berardi alessandro</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>vqZMiS0h</t>
+          <t>6TtQuJeb</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>illic ivan</t>
+          <t>guilbert frederic</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>4vTK4LUr</t>
+          <t>4jKQUIgi</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sosa borna</t>
+          <t>hasa luis</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>nRc0fR5f</t>
+          <t>lIjZ6yI2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>tameze adrien</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+          <t>kaba mohamed</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>bygrxvpg</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>marchwinski filip</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>OYhxyduf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>abraham tammy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KS8ySjGG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sl6O3rbN</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>gabbia matteo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ATurLHr0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>hernandez theo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0Qcw6Yy1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>lobotka stanislav</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EBsz2tTd</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>meret alex</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CnvwSKf9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>rui mario</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4fbjCD7B</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>berisha medon</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>GxXIRkFl</t>
+          <t>UgYYWt1i</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>gallo antonino</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0xAp4q1P</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>gonzalez joan</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>8xArOHfB</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>sansone nicola</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>IoRXiRdq</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>banda lameck</t>
-        </is>
-      </c>
+          <t>spinazzola leonardo</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>SE59rbUO</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>bonifazi kevin</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>vVyq9D0S</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>burnete catalin</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>4jKQUIgi</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>hasa luis</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>lIjZ6yI2</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>bygrxvpg</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>marchwinski filip</t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>viIS0FT7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>jovic luka</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>f17EnPl3</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>reijnders tijani</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>OKPvQBOR</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>calabria davide</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lt87Q6nj</t>
+          <t>KbPlg3Fl</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brescianini marco</t>
+          <t>ebuehi tyronne</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SzDIipZ9</t>
+          <t>QiCirDVf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>kossounou odilon</t>
+          <t>belardinelli luca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hvC4gron</t>
+          <t>WrbP1Sdg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>scalvini giorgio</t>
+          <t>esposito sebastiano</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>vDgQxOYl</t>
+          <t>CnRzW1VM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>scamacca gianluca</t>
+          <t>maleh youssef</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>QB1RMomj</t>
+          <t>6HUZxS6p</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>toloi rafael</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>perisan samuele</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ImoJ2c3M</t>
+          <t>SrhnSpzL</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>cruz juan</t>
+          <t>acerbi francesco</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6JBYdeU4</t>
+          <t>IRQeP5FJ</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>duda ondrej</t>
+          <t>calhanoglu hakan</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CERvOK0k</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>frese martin</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>nJ2Rd9i9</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>harroui abdou</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>AZfDAIPf</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>alidou faride</t>
-        </is>
-      </c>
+          <t>carlos augusto</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Ees7JNmc</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>hh5m41l6</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>dawidowicz pawel</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>A1vJjksK</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>lambourde mathis</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>WrzFSvEm</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>serdar suat</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KSn7To32</t>
+          <t>tpMja0bC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>benedyczak adrian</t>
+          <t>bjarkason bjarki steinn</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>x0EJsbc8</t>
+          <t>h6p8JLua</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>circati alessandro</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>6NqFKJLp</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>estevez nahuel</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>WU5civJO</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>kowalski mateusz</t>
-        </is>
-      </c>
+          <t>sverko marin</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>KbPlg3Fl</t>
+          <t>GdjB2qGA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ebuehi tyronne</t>
+          <t>kristensen thomas</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>t2MszR74</t>
+          <t>QgGt7V0d</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>sazonov saba</t>
+          <t>sanchez alexis</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>QiCirDVf</t>
+          <t>SMbMSc26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>belardinelli luca</t>
+          <t>thauvin florian</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CnRzW1VM</t>
+          <t>Y3ooARhm</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>maleh youssef</t>
+          <t>atta arthur</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>6HUZxS6p</t>
+          <t>ChzBGkMR</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>perisan samuele</t>
+          <t>payero martin</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1334,272 +1256,268 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Ees7JNmc</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>zurkowski szymon</t>
-        </is>
-      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6ZesE86o</t>
+          <t>lt87Q6nj</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>guendouzi matteo</t>
+          <t>brescianini marco</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WlqJxlIT</t>
+          <t>SzDIipZ9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>lazzari manuel</t>
+          <t>kossounou odilon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wr49C0j4</t>
+          <t>hvC4gron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>romagnoli alessio</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ABbkAWNr</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bondo warren</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CtdcoETk</t>
+          <t>p8mcxZnq</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ekuban caleb</t>
+          <t>ciurria patrick</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>GGkyU0bT</t>
+          <t>ENDYjGK9</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>malinovsky ruslan</t>
+          <t>cragno alessio</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>8l36RdAF</t>
+          <t>lb7jSwtb</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>messias junior</t>
+          <t>birindelli samuele</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>AazXYT3h</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>vitinha</t>
+          <t>gagliardini roberto</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4InuIizr</t>
+          <t>txSCnXec</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>badelj milan</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+          <t>maldini daniel</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>MRq91oVQ</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>petagna andrea</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>vgmL526e</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>bani mattia</t>
-        </is>
-      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>EFmPm0Qo</t>
+          <t>dbqlLrFU</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>de winter koni</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>vZY7FZwP</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>gollini pierluigi</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>63jp0ZJd</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>norton cuffy brooke</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+          <t>sensi stefano</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>p8mcxZnq</t>
+          <t>INWVBb0R</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ciurria patrick</t>
+          <t>bremer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ENDYjGK9</t>
+          <t>filNjPIq</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>cragno alessio</t>
+          <t>gonzalez nicolas ivan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>f1Ft78yl</t>
+          <t>EskCwiLE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>gagliardini roberto</t>
+          <t>milik arkadiusz</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>txSCnXec</t>
+          <t>MTNGv0hT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>maldini daniel</t>
+          <t>pogba paul</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>MRq91oVQ</t>
+          <t>IZxlmmuF</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>petagna andrea</t>
+          <t>douglas luiz</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dbqlLrFU</t>
+          <t>KSn7To32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sensi stefano</t>
+          <t>benedyczak adrian</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>tpMja0bC</t>
+          <t>x0EJsbc8</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bjarkason bjarki steinn</t>
+          <t>circati alessandro</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>tjm4dqgg</t>
+          <t>6NqFKJLp</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>duncan alfred</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>WU5civJO</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>kowalski mateusz</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>48K74eTp</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>osorio yordan</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>GdRRPoEK</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>turati stefano</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>lOCjQkeo</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>koopmeiners teun</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
@@ -1608,234 +1526,254 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SrhnSpzL</t>
+          <t>CtdcoETk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>acerbi francesco</t>
+          <t>ekuban caleb</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>G62SXlFI</t>
+          <t>GGkyU0bT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>buchanan tajon</t>
+          <t>malinovsky ruslan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IRQeP5FJ</t>
+          <t>8l36RdAF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>calhanoglu hakan</t>
+          <t>messias junior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>QZQkZOWj</t>
+          <t>AazXYT3h</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>carlos augusto</t>
+          <t>vitinha</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hzUi0u2S</t>
+          <t>4InuIizr</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>asllani kristjan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bHCOu1Tl</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gudmundsson albert</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>INWVBb0R</t>
+          <t>OSXlKkv9</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>bremer</t>
+          <t>pongracic marin</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>EskCwiLE</t>
+          <t>QPclX9Uq</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>IZxlmmuF</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>douglas luiz</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>filNjPIq</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>gonzalez nicolas ivan</t>
-        </is>
-      </c>
+          <t>kean moise</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>vgmL526e</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>bani mattia</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EFmPm0Qo</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>de winter koni</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>vZY7FZwP</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>gollini pierluigi</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>lOCjQkeo</t>
+          <t>63jp0ZJd</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>koopmeiners teun</t>
+          <t>norton cuffy brooke</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bHCOu1Tl</t>
+          <t>fFLge2V1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gudmundsson albert</t>
+          <t>el shaarawy stephan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>v9oBM840</t>
+          <t>OUjnz4Ab</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>mandragora rolando</t>
+          <t>hermoso mario</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OSXlKkv9</t>
+          <t>n5cPVwks</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pongracic marin</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>QPclX9Uq</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>kean moise</t>
-        </is>
-      </c>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CS7XFNwq</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ilkhan emirhan</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>fFLge2V1</t>
+          <t>bmU7ExmH</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>el shaarawy stephan</t>
+          <t>savva zannetos</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>n5cPVwks</t>
+          <t>ARdXOcOJ</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>saelemaekers alexis</t>
+          <t>schuurs perr</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>W4myUVXR</t>
+          <t>v7zQxVoD</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>dybala paulo</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+          <t>zapata duvan</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>vqZMiS0h</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>illic ivan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>vwnI8wkF</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>nije eybi</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4vTK4LUr</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>sosa borna</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
@@ -1844,14 +1782,909 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>nRc0fR5f</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>tameze adrien</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KSz457vB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>barba federico</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IBUaxPl6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>cerri alberto</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Uaabio2H</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>van der brempt ignace</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>WlqJxlIT</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lazzari manuel</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,592 +501,304 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_9</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_9</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_8</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_8</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MiXFJwit</t>
+          <t>CtdcoETk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>aebischer michel</t>
+          <t>ekuban caleb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>80NWC6K6</t>
+          <t>GGkyU0bT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cambiaghi nicolo</t>
+          <t>malinovsky ruslan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8CI4QAT5</t>
+          <t>8l36RdAF</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>el azzouzi oussama</t>
+          <t>messias junior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>n9FYAE96</t>
+          <t>AazXYT3h</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>erlic martin</t>
+          <t>vitinha</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Q995M7Dt</t>
+          <t>fTOU6yR2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ferguson lewis</t>
+          <t>ankeye david</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EmmpFCXN</t>
+          <t>vgmL526e</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ndoye dan</t>
+          <t>bani mattia</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hxdzXUCO</t>
+          <t>EFmPm0Qo</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>lykogiannis charalampos</t>
+          <t>de winter koni</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0xAp4q1P</t>
+          <t>vZY7FZwP</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>gonzalez joan</t>
+          <t>gollini pierluigi</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>8xArOHfB</t>
+          <t>63jp0ZJd</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>sansone nicola</t>
+          <t>norton cuffy brooke</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4fbjCD7B</t>
+          <t>KSz457vB</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>berisha medon</t>
+          <t>barba federico</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>SE59rbUO</t>
+          <t>IBUaxPl6</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>bonifazi kevin</t>
+          <t>cerri alberto</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>vVyq9D0S</t>
+          <t>vmcGpMJM</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>burnete catalin</t>
+          <t>perrone maximo</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6TtQuJeb</t>
+          <t>W2R804U4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>guilbert frederic</t>
+          <t>roberto sergi</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>4jKQUIgi</t>
+          <t>Uaabio2H</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hasa luis</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lIjZ6yI2</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>kaba mohamed</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>bygrxvpg</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>marchwinski filip</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+          <t>van der brempt ignace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>WpIsmaGl</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deulofeu gerard</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GdjB2qGA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>kristensen thomas</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SMbMSc26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>thauvin florian</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>jaNZBJgT</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>toure souleymane</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Y3ooARhm</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>atta arthur</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ChzBGkMR</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>payero martin</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>QgGt7V0d</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>INWVBb0R</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>bremer</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>IZxlmmuF</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>douglas luiz</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>filNjPIq</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>gonzalez nicolas ivan</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>EskCwiLE</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>milik arkadiusz</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>MTNGv0hT</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>pogba paul</t>
-        </is>
-      </c>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>p8mcxZnq</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ciurria patrick</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ENDYjGK9</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>cragno alessio</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>lb7jSwtb</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>birindelli samuele</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>f1Ft78yl</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>gagliardini roberto</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>txSCnXec</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>maldini daniel</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MRq91oVQ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>petagna andrea</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>dbqlLrFU</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>sensi stefano</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>OYhxyduf</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>abraham tammy</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>KS8ySjGG</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>bennacer ismael</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>8UwHPuvH</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>florenzi alessandro</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Sl6O3rbN</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>gabbia matteo</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>viIS0FT7</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>jovic luka</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>OKPvQBOR</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>calabria davide</t>
-        </is>
-      </c>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CnvwSKf9</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>rui mario</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0Qcw6Yy1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>lobotka stanislav</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>UgYYWt1i</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>spinazzola leonardo</t>
-        </is>
-      </c>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1095,165 +807,47 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>lt87Q6nj</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>brescianini marco</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>SzDIipZ9</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>kossounou odilon</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>hvC4gron</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>scalvini giorgio</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>vDgQxOYl</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>scamacca gianluca</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CS7XFNwq</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ilkhan emirhan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>bmU7ExmH</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>savva zannetos</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ARdXOcOJ</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>schuurs perr</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>v7zQxVoD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>zapata duvan</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>vqZMiS0h</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>illic ivan</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>vwnI8wkF</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>nije eybi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>nRc0fR5f</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>tameze adrien</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>bHCOu1Tl</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>gudmundsson albert</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>QPclX9Uq</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>kean moise</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>OSXlKkv9</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>pongracic marin</t>
-        </is>
-      </c>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1262,109 +856,31 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>8vDirdIn</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>belahyane reda</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ImoJ2c3M</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>cruz juan</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>hh5m41l6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>dawidowicz pawel</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CERvOK0k</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>frese martin</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>nJ2Rd9i9</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>harroui abdou</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>6w5hZnnM</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>tchatchoua jackson</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>AZfDAIPf</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>alidou faride</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>n5cPVwks</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>saelemaekers alexis</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>fFLge2V1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>el shaarawy stephan</t>
-        </is>
-      </c>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1375,57 +891,19 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>nuvpd81D</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>berardi alessandro</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>G62SXlFI</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>buchanan tajon</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IRQeP5FJ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>calhanoglu hakan</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>QZQkZOWj</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>carlos augusto</t>
-        </is>
-      </c>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1434,26 +912,10 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>tpMja0bC</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>bjarkason bjarki steinn</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>h6p8JLua</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>sverko marin</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1464,17 +926,11 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1505,17 +961,11 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1546,17 +996,11 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1587,12 +1031,6 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,164 +569,232 @@
           <t>player_name_miss_away_5</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CtdcoETk</t>
+          <t>4fbjCD7B</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ekuban caleb</t>
+          <t>berisha medon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GGkyU0bT</t>
+          <t>0xAp4q1P</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>malinovsky ruslan</t>
+          <t>gonzalez joan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8l36RdAF</t>
+          <t>lIjZ6yI2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>messias junior</t>
+          <t>kaba mohamed</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AazXYT3h</t>
+          <t>fZXLQLKC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>vitinha</t>
+          <t>pierret balthazar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>8xArOHfB</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>sansone nicola</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>vgmL526e</t>
+          <t>SE59rbUO</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bani mattia</t>
+          <t>bonifazi kevin</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>EFmPm0Qo</t>
+          <t>vVyq9D0S</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>de winter koni</t>
+          <t>burnete catalin</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>vZY7FZwP</t>
+          <t>4jKQUIgi</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>gollini pierluigi</t>
+          <t>hasa luis</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>63jp0ZJd</t>
+          <t>bygrxvpg</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>norton cuffy brooke</t>
+          <t>marchwinski filip</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KSz457vB</t>
+          <t>KbPlg3Fl</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>barba federico</t>
+          <t>ebuehi tyronne</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>IBUaxPl6</t>
+          <t>WrbP1Sdg</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>cerri alberto</t>
+          <t>esposito sebastiano</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>vmcGpMJM</t>
+          <t>b3uylvFN</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>perrone maximo</t>
+          <t>fazzini jacopo</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>W2R804U4</t>
+          <t>E7Jj74nK</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>roberto sergi</t>
+          <t>grassi alberto</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Uaabio2H</t>
+          <t>6HUZxS6p</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>van der brempt ignace</t>
-        </is>
-      </c>
+          <t>perisan samuele</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Ees7JNmc</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>h6p8JLua</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sverko marin</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -741,29 +809,115 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Qw9q7XhE</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>bernabe adrian</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>WU5civJO</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>kowalski mateusz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>bcZkPxo4</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>hernani</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>48K74eTp</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>osorio yordan</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>thWJbHFE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>adopo michel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0hqx5eWc</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mina yerry</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tvxzDyfa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>mutandwa kingstone</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -776,31 +930,101 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>KS8ySjGG</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Sl6O3rbN</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>gabbia matteo</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>fmkHs3aU</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>morata alvaro</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INWVBb0R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bremer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>filNjPIq</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>gonzalez nicolas ivan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EskCwiLE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>milik arkadiusz</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MTNGv0hT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pogba paul</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -811,29 +1035,99 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CS7XFNwq</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>ilkhan emirhan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>bmU7ExmH</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>savva zannetos</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>v7zQxVoD</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>zapata duvan</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>vqZMiS0h</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>illic ivan</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8xFYnbEi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kolasinac sead</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>hvC4gron</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>scalvini giorgio</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>vDgQxOYl</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>scamacca gianluca</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -846,29 +1140,99 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>GdjB2qGA</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>kristensen thomas</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SMbMSc26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>thauvin florian</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OUjnz4Ab</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>hermoso mario</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0ORJzjri</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>n dicka obite</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -881,27 +1245,89 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>MiXFJwit</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>aebischer michel</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>80NWC6K6</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>cambiaghi nicolo</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>8CI4QAT5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>el azzouzi oussama</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>n9FYAE96</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>erlic martin</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Q995M7Dt</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ferguson lewis</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bHCOu1Tl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gudmundsson albert</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IcuAZWW1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>cataldi danilo</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -916,43 +1342,169 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ImoJ2c3M</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>cruz juan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>hh5m41l6</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>dawidowicz pawel</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CERvOK0k</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>frese martin</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Aiy63dji</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>rocha livramento dailon</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>AZfDAIPf</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>alidou faride</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>nuvpd81D</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>berardi alessandro</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>nJ2Rd9i9</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>harroui abdou</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>fuwlkDxt</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>okou yllan</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>p8mcxZnq</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ciurria patrick</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ENDYjGK9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>cragno alessio</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>lb7jSwtb</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>birindelli samuele</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>f1Ft78yl</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>gagliardini roberto</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MRq91oVQ</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>petagna andrea</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dbqlLrFU</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sensi stefano</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ALBpOZPH</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>castrovilli gaetano</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -961,19 +1513,49 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>QZQkZOWj</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>carlos augusto</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hzUi0u2S</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>asllani kristjan</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -986,21 +1568,51 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0Qcw6Yy1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>lobotka stanislav</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>CnvwSKf9</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>rui mario</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>UgYYWt1i</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>spinazzola leonardo</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1031,6 +1643,53 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
